--- a/Data.xlsx
+++ b/Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\Economic-Newsletter\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\Dashboard_Deployed\Monthly-Newsletter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C6A9D6-A246-47B4-BE1A-C0543E8EB609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DAF5734-ECE2-4772-BC5D-FC6B74DBC8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8E035F72-D6B3-4207-8637-DB24C6D06A30}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{8E035F72-D6B3-4207-8637-DB24C6D06A30}"/>
   </bookViews>
   <sheets>
     <sheet name="2001-only" sheetId="1" r:id="rId1"/>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>CoPS</t>
-  </si>
-  <si>
-    <t>BDC</t>
   </si>
   <si>
     <t>M3</t>
@@ -121,6 +118,9 @@
   </si>
   <si>
     <t>Transportation CPI</t>
+  </si>
+  <si>
+    <t>Exchange Rate</t>
   </si>
 </sst>
 </file>
@@ -553,25 +553,25 @@
         <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="8" t="s">
-        <v>23</v>
-      </c>
       <c r="N1" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -13866,19 +13866,19 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>22</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -25621,34 +25621,34 @@
         <v>6</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="N1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>24</v>
-      </c>
       <c r="Q1" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -33437,46 +33437,46 @@
         <v>6</v>
       </c>
       <c r="H1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>22</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
@@ -33505,7 +33505,7 @@
         <v>430812.78909999999</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N2">
         <v>29.38</v>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\Dashboard_Deployed\Monthly-Newsletter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DAF5734-ECE2-4772-BC5D-FC6B74DBC8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEEF971D-40D4-4511-99C2-EA6DD49B54E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{8E035F72-D6B3-4207-8637-DB24C6D06A30}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{8E035F72-D6B3-4207-8637-DB24C6D06A30}"/>
   </bookViews>
   <sheets>
     <sheet name="2001-only" sheetId="1" r:id="rId1"/>
@@ -187,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -202,6 +202,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -516,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{446A3700-1DFF-4FC6-84A1-7C9F77253BFC}">
-  <dimension ref="A1:O261"/>
+  <dimension ref="A1:O262"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -13830,6 +13831,53 @@
         <v>409.1</v>
       </c>
     </row>
+    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A262" s="2">
+        <v>44805</v>
+      </c>
+      <c r="B262">
+        <v>93.25</v>
+      </c>
+      <c r="C262">
+        <v>5.68</v>
+      </c>
+      <c r="D262">
+        <v>15.5</v>
+      </c>
+      <c r="E262">
+        <v>21188070.109999999</v>
+      </c>
+      <c r="F262">
+        <v>40503824.530000001</v>
+      </c>
+      <c r="G262">
+        <v>49316901.829999998</v>
+      </c>
+      <c r="H262">
+        <v>27701274.760000002</v>
+      </c>
+      <c r="I262" s="4">
+        <v>810</v>
+      </c>
+      <c r="J262" s="4">
+        <v>20.763674933077418</v>
+      </c>
+      <c r="K262" s="4">
+        <v>23.336929408424744</v>
+      </c>
+      <c r="L262" s="4">
+        <v>16.434588773412841</v>
+      </c>
+      <c r="M262" s="4">
+        <v>18.743389646399677</v>
+      </c>
+      <c r="N262">
+        <v>564.4</v>
+      </c>
+      <c r="O262">
+        <v>415.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13837,7 +13885,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F39A23B-C6C5-4BDE-A8B5-41DEB2B21623}">
-  <dimension ref="A1:M261"/>
+  <dimension ref="A1:M262"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -25575,6 +25623,47 @@
       </c>
       <c r="M261">
         <v>18.254082959965324</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A262" s="2">
+        <v>44805</v>
+      </c>
+      <c r="B262">
+        <v>93.25</v>
+      </c>
+      <c r="C262">
+        <v>5.68</v>
+      </c>
+      <c r="D262">
+        <v>15.5</v>
+      </c>
+      <c r="E262">
+        <v>21188070.109999999</v>
+      </c>
+      <c r="F262">
+        <v>40503824.530000001</v>
+      </c>
+      <c r="G262">
+        <v>49316901.829999998</v>
+      </c>
+      <c r="H262">
+        <v>27701274.760000002</v>
+      </c>
+      <c r="I262" s="12">
+        <v>810</v>
+      </c>
+      <c r="J262" s="4">
+        <v>20.763674933077418</v>
+      </c>
+      <c r="K262" s="4">
+        <v>23.336929408424744</v>
+      </c>
+      <c r="L262" s="4">
+        <v>16.434588773412841</v>
+      </c>
+      <c r="M262" s="4">
+        <v>18.743389646399677</v>
       </c>
     </row>
   </sheetData>
@@ -25584,7 +25673,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B7C967-F799-47E9-8E6B-28B0445D2871}">
-  <dimension ref="A1:Q137"/>
+  <dimension ref="A1:Q138"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -33397,6 +33486,50 @@
       </c>
       <c r="Q137" s="4">
         <v>124</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A138" s="10">
+        <v>44805</v>
+      </c>
+      <c r="B138">
+        <v>93.25</v>
+      </c>
+      <c r="C138">
+        <v>5.68</v>
+      </c>
+      <c r="D138">
+        <v>15.5</v>
+      </c>
+      <c r="E138">
+        <v>21188070.109999999</v>
+      </c>
+      <c r="F138">
+        <v>40503824.530000001</v>
+      </c>
+      <c r="G138">
+        <v>49316901.829999998</v>
+      </c>
+      <c r="H138">
+        <v>27701274.760000002</v>
+      </c>
+      <c r="I138" s="12">
+        <v>810</v>
+      </c>
+      <c r="J138" s="4">
+        <v>20.763674933077418</v>
+      </c>
+      <c r="K138" s="4">
+        <v>23.336929408424744</v>
+      </c>
+      <c r="L138" s="4">
+        <v>16.434588773412841</v>
+      </c>
+      <c r="M138" s="4">
+        <v>18.743389646399677</v>
+      </c>
+      <c r="N138">
+        <v>49932982.310000002</v>
       </c>
     </row>
   </sheetData>
@@ -50461,7 +50594,7 @@
         <v>409.1</v>
       </c>
       <c r="R273">
-        <f t="shared" ref="R273:R276" si="21">(N273-N261)/N261*100</f>
+        <f t="shared" ref="R273:S276" si="21">(N273-N261)/N261*100</f>
         <v>20.51701236333912</v>
       </c>
       <c r="S273">
@@ -50478,21 +50611,63 @@
       </c>
     </row>
     <row r="274" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A274" s="2">
+        <v>44805</v>
+      </c>
+      <c r="B274">
+        <v>93.25</v>
+      </c>
+      <c r="C274">
+        <v>5.68</v>
+      </c>
+      <c r="D274">
+        <v>15.5</v>
+      </c>
+      <c r="E274">
+        <v>21188070.109999999</v>
+      </c>
+      <c r="F274">
+        <v>40503824.530000001</v>
+      </c>
+      <c r="G274">
+        <v>49316901.829999998</v>
+      </c>
+      <c r="H274">
+        <v>27701274.760000002</v>
+      </c>
+      <c r="I274">
+        <v>49932982.310000002</v>
+      </c>
+      <c r="M274" s="4">
+        <v>810</v>
+      </c>
+      <c r="N274">
+        <v>478.2</v>
+      </c>
+      <c r="O274">
+        <v>564.4</v>
+      </c>
+      <c r="P274">
+        <v>402.2</v>
+      </c>
+      <c r="Q274">
+        <v>415.4</v>
+      </c>
       <c r="R274">
         <f t="shared" si="21"/>
-        <v>-100</v>
+        <v>20.763674933077418</v>
       </c>
       <c r="S274">
-        <f t="shared" ref="S274:S276" si="24">(O274-O262)/O262*100</f>
-        <v>-100</v>
+        <f t="shared" si="21"/>
+        <v>23.336929408424744</v>
       </c>
       <c r="T274">
         <f t="shared" si="22"/>
-        <v>-100</v>
+        <v>16.434588773412841</v>
       </c>
       <c r="U274">
         <f t="shared" si="23"/>
-        <v>-100</v>
+        <v>18.743389646399677</v>
       </c>
     </row>
     <row r="275" spans="1:21" x14ac:dyDescent="0.25">
@@ -50501,7 +50676,7 @@
         <v>-100</v>
       </c>
       <c r="S275">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="S274:S276" si="24">(O275-O263)/O263*100</f>
         <v>-100</v>
       </c>
       <c r="T275">

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\Dashboard_Deployed\Monthly-Newsletter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEEF971D-40D4-4511-99C2-EA6DD49B54E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7822401-2D4D-4616-BEA0-E113DED50E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{8E035F72-D6B3-4207-8637-DB24C6D06A30}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{8E035F72-D6B3-4207-8637-DB24C6D06A30}"/>
   </bookViews>
   <sheets>
     <sheet name="2001-only" sheetId="1" r:id="rId1"/>
@@ -33531,6 +33531,15 @@
       <c r="N138">
         <v>49932982.310000002</v>
       </c>
+      <c r="O138" s="6">
+        <v>0</v>
+      </c>
+      <c r="P138" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q138" s="4">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -50676,7 +50685,7 @@
         <v>-100</v>
       </c>
       <c r="S275">
-        <f t="shared" ref="S274:S276" si="24">(O275-O263)/O263*100</f>
+        <f t="shared" ref="S275:S276" si="24">(O275-O263)/O263*100</f>
         <v>-100</v>
       </c>
       <c r="T275">
